--- a/temp/espc-2/searchByMAC-6.xlsx
+++ b/temp/espc-2/searchByMAC-6.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="41">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>17.48</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -516,15 +519,21 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>

--- a/temp/espc-2/searchByMAC-6.xlsx
+++ b/temp/espc-2/searchByMAC-6.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="47">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -137,6 +137,24 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>6.2.17</t>
+  </si>
+  <si>
+    <t>6.2.16</t>
+  </si>
+  <si>
+    <t>6.2.23</t>
+  </si>
+  <si>
+    <t>6.2.22</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -487,13 +505,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB211"/>
+  <dimension ref="A1:AH211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +531,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -537,7 +555,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -557,7 +575,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -578,8 +596,14 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R4">
+        <v>12</v>
+      </c>
+      <c r="AA4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -600,8 +624,22 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" s="1"/>
+      <c r="AB5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD5" s="1"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -622,8 +660,22 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U6" s="1"/>
+      <c r="AB6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD6" s="1"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -644,8 +696,22 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U7" s="1"/>
+      <c r="AB7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD7" s="1"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
@@ -666,8 +732,22 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U8" s="1"/>
+      <c r="AB8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD8" s="1"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -688,8 +768,22 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U9" s="1"/>
+      <c r="AB9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD9" s="1"/>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -710,8 +804,32 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R10">
+        <v>11</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA10">
+        <v>11</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
@@ -732,8 +850,26 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -754,8 +890,38 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -776,8 +942,38 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -798,8 +994,38 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R14">
+        <v>11</v>
+      </c>
+      <c r="S14" s="1">
+        <v>6</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA14">
+        <v>11</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>6</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -820,8 +1046,32 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>13</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
@@ -842,8 +1092,26 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -860,8 +1128,38 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -880,8 +1178,44 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
@@ -902,8 +1236,50 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R19">
+        <v>11</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA19">
+        <v>11</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
@@ -924,8 +1300,50 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG20" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
@@ -946,8 +1364,56 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA21">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH21" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
@@ -968,8 +1434,56 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
@@ -991,7 +1505,7 @@
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
@@ -1012,8 +1526,14 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R24">
+        <v>12</v>
+      </c>
+      <c r="AA24">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
@@ -1034,8 +1554,22 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U25" s="1"/>
+      <c r="AB25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD25" s="1"/>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
@@ -1056,8 +1590,22 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U26" s="1"/>
+      <c r="AB26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD26" s="1"/>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
@@ -1078,8 +1626,22 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U27" s="1"/>
+      <c r="AB27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD27" s="1"/>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
@@ -1100,8 +1662,22 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U28" s="1"/>
+      <c r="AB28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD28" s="1"/>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
@@ -1122,8 +1698,22 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U29" s="1"/>
+      <c r="AB29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD29" s="1"/>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
@@ -1144,8 +1734,14 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
@@ -1166,8 +1762,26 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD31" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1184,8 +1798,16 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>17</v>
@@ -1210,8 +1832,20 @@
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
@@ -1240,8 +1874,26 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE34" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
@@ -1271,7 +1923,7 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
@@ -1301,7 +1953,7 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
@@ -1323,7 +1975,7 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
@@ -1349,7 +2001,7 @@
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
@@ -1379,7 +2031,7 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
@@ -1401,7 +2053,7 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
@@ -1423,7 +2075,7 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
@@ -1453,7 +2105,7 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
@@ -1479,7 +2131,7 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
@@ -1501,7 +2153,7 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
@@ -1523,7 +2175,7 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
@@ -1557,7 +2209,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1575,7 +2227,7 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>16</v>

--- a/temp/espc-2/searchByMAC-6.xlsx
+++ b/temp/espc-2/searchByMAC-6.xlsx
@@ -1128,6 +1128,9 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
+      <c r="R17">
+        <v>11</v>
+      </c>
       <c r="S17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,6 +1145,9 @@
       </c>
       <c r="W17" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="AA17">
+        <v>11</v>
       </c>
       <c r="AB17" s="1" t="s">
         <v>14</v>
